--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/77.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/77.xlsx
@@ -426,13 +426,13 @@
         <v>-4.907487902926885</v>
       </c>
       <c r="E2">
-        <v>-6.1234434671202</v>
+        <v>-8.989736577626045</v>
       </c>
       <c r="F2">
-        <v>-3.031499293104398</v>
+        <v>-3.916729147901673</v>
       </c>
       <c r="G2">
-        <v>-8.679564745311843</v>
+        <v>-9.479410733457447</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.392275809922014</v>
       </c>
       <c r="E3">
-        <v>-6.618630853379508</v>
+        <v>-9.277018358175761</v>
       </c>
       <c r="F3">
-        <v>-2.932765353997322</v>
+        <v>-3.982107216800221</v>
       </c>
       <c r="G3">
-        <v>-8.2860289378812</v>
+        <v>-9.405071086597792</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.780970927833607</v>
       </c>
       <c r="E4">
-        <v>-6.85775199540651</v>
+        <v>-10.07796931538027</v>
       </c>
       <c r="F4">
-        <v>-3.110333362094021</v>
+        <v>-4.065111287295538</v>
       </c>
       <c r="G4">
-        <v>-8.016413427840044</v>
+        <v>-8.624462369971805</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.175643118173893</v>
       </c>
       <c r="E5">
-        <v>-6.911648218768811</v>
+        <v>-10.74674847538344</v>
       </c>
       <c r="F5">
-        <v>-2.522086475078814</v>
+        <v>-3.726991594290446</v>
       </c>
       <c r="G5">
-        <v>-8.300478103820716</v>
+        <v>-8.548718142522132</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.58845906304182</v>
       </c>
       <c r="E6">
-        <v>-8.596979842270985</v>
+        <v>-11.76584685742456</v>
       </c>
       <c r="F6">
-        <v>-2.274662243904033</v>
+        <v>-3.767472252530452</v>
       </c>
       <c r="G6">
-        <v>-7.798361428845671</v>
+        <v>-7.972287928133342</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.055213403955121</v>
       </c>
       <c r="E7">
-        <v>-9.689689741833375</v>
+        <v>-12.39442708501471</v>
       </c>
       <c r="F7">
-        <v>-2.671855301504965</v>
+        <v>-3.415183335100476</v>
       </c>
       <c r="G7">
-        <v>-7.809414016072149</v>
+        <v>-7.874759647815419</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.579489331844306</v>
       </c>
       <c r="E8">
-        <v>-9.799965808930221</v>
+        <v>-12.68013479847232</v>
       </c>
       <c r="F8">
-        <v>-2.567557218553285</v>
+        <v>-3.815288932489651</v>
       </c>
       <c r="G8">
-        <v>-7.347521083012387</v>
+        <v>-7.248263184402851</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.165479640760779</v>
       </c>
       <c r="E9">
-        <v>-10.71980244030795</v>
+        <v>-13.77412388712276</v>
       </c>
       <c r="F9">
-        <v>-2.387407189262059</v>
+        <v>-3.289710524598435</v>
       </c>
       <c r="G9">
-        <v>-6.712650656323822</v>
+        <v>-7.133894296099951</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.8031859730515727</v>
       </c>
       <c r="E10">
-        <v>-11.33919161123625</v>
+        <v>-13.82217654215102</v>
       </c>
       <c r="F10">
-        <v>-2.252380817503532</v>
+        <v>-3.610042684363212</v>
       </c>
       <c r="G10">
-        <v>-5.657066571011125</v>
+        <v>-6.102514423891465</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.483878411164193</v>
       </c>
       <c r="E11">
-        <v>-12.18920445382096</v>
+        <v>-14.77277185660043</v>
       </c>
       <c r="F11">
-        <v>-2.118799946862889</v>
+        <v>-3.433833198807104</v>
       </c>
       <c r="G11">
-        <v>-5.378460961970471</v>
+        <v>-5.822274488736774</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.2084920061942068</v>
       </c>
       <c r="E12">
-        <v>-13.21541728686152</v>
+        <v>-15.39967418681535</v>
       </c>
       <c r="F12">
-        <v>-1.86607416431019</v>
+        <v>-3.499377769553615</v>
       </c>
       <c r="G12">
-        <v>-4.715867038468875</v>
+        <v>-4.983844306279106</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.01601432378039612</v>
       </c>
       <c r="E13">
-        <v>-14.01488139441174</v>
+        <v>-16.69963763790933</v>
       </c>
       <c r="F13">
-        <v>-1.987752223740007</v>
+        <v>-3.558220019644075</v>
       </c>
       <c r="G13">
-        <v>-4.9760903948435</v>
+        <v>-4.726161204391635</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.1712589207964491</v>
       </c>
       <c r="E14">
-        <v>-14.45451957920147</v>
+        <v>-16.91639373695213</v>
       </c>
       <c r="F14">
-        <v>-2.040133208088631</v>
+        <v>-3.323499630958627</v>
       </c>
       <c r="G14">
-        <v>-4.444589789495475</v>
+        <v>-4.137897790143624</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.2456903846595044</v>
       </c>
       <c r="E15">
-        <v>-15.16130062282681</v>
+        <v>-18.45559046677889</v>
       </c>
       <c r="F15">
-        <v>-1.436771929441944</v>
+        <v>-3.322122884335174</v>
       </c>
       <c r="G15">
-        <v>-3.809212878356235</v>
+        <v>-3.622706506256284</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.237586210150082</v>
       </c>
       <c r="E16">
-        <v>-16.86162533921162</v>
+        <v>-19.15365807304475</v>
       </c>
       <c r="F16">
-        <v>-0.7111361668354246</v>
+        <v>-2.89320915377884</v>
       </c>
       <c r="G16">
-        <v>-2.94384242246287</v>
+        <v>-3.670976563001378</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.1612704511983518</v>
       </c>
       <c r="E17">
-        <v>-18.00252910298732</v>
+        <v>-19.58144299271341</v>
       </c>
       <c r="F17">
-        <v>-1.168541594211047</v>
+        <v>-2.819256653893914</v>
       </c>
       <c r="G17">
-        <v>-2.729959782580505</v>
+        <v>-2.961323968244964</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.04592105772805862</v>
       </c>
       <c r="E18">
-        <v>-18.87174639473803</v>
+        <v>-20.14513344656444</v>
       </c>
       <c r="F18">
-        <v>-1.35359970036386</v>
+        <v>-2.863052438479924</v>
       </c>
       <c r="G18">
-        <v>-1.922412097891117</v>
+        <v>-3.395660492145526</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.07533154614941397</v>
       </c>
       <c r="E19">
-        <v>-18.84242472278475</v>
+        <v>-21.0617637987994</v>
       </c>
       <c r="F19">
-        <v>-0.7633605897449194</v>
+        <v>-2.508580772943571</v>
       </c>
       <c r="G19">
-        <v>-1.679453595497523</v>
+        <v>-3.038252168366708</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.1695392579673939</v>
       </c>
       <c r="E20">
-        <v>-20.21375280407326</v>
+        <v>-21.920456853053</v>
       </c>
       <c r="F20">
-        <v>-0.8585201235089154</v>
+        <v>-2.409663764640476</v>
       </c>
       <c r="G20">
-        <v>-1.718100447679773</v>
+        <v>-2.427685163076817</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.2146641673696744</v>
       </c>
       <c r="E21">
-        <v>-21.22952861705452</v>
+        <v>-22.59118386916751</v>
       </c>
       <c r="F21">
-        <v>-0.2254072012232812</v>
+        <v>-1.827952696433357</v>
       </c>
       <c r="G21">
-        <v>-1.456355027208528</v>
+        <v>-2.574769291850958</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.1995621556413451</v>
       </c>
       <c r="E22">
-        <v>-21.06761982676741</v>
+        <v>-23.18465284821756</v>
       </c>
       <c r="F22">
-        <v>-0.668847182555107</v>
+        <v>-2.076542440543878</v>
       </c>
       <c r="G22">
-        <v>-1.751212521328863</v>
+        <v>-2.918959415764969</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.1275557295782237</v>
       </c>
       <c r="E23">
-        <v>-20.73608973276297</v>
+        <v>-23.02664807657578</v>
       </c>
       <c r="F23">
-        <v>-0.2975190687391866</v>
+        <v>-1.842299191482442</v>
       </c>
       <c r="G23">
-        <v>-0.8854843934265151</v>
+        <v>-2.489520648717336</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.01365066085393859</v>
       </c>
       <c r="E24">
-        <v>-21.10998673549198</v>
+        <v>-23.58314932162353</v>
       </c>
       <c r="F24">
-        <v>-0.05429466029659855</v>
+        <v>-1.366175974273162</v>
       </c>
       <c r="G24">
-        <v>-0.6984558724083415</v>
+        <v>-2.847696531405941</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.120066696408928</v>
       </c>
       <c r="E25">
-        <v>-22.44900698588465</v>
+        <v>-23.70803638616113</v>
       </c>
       <c r="F25">
-        <v>0.05586080856027691</v>
+        <v>-1.514637636937695</v>
       </c>
       <c r="G25">
-        <v>-1.674031078981781</v>
+        <v>-2.617052911248629</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2512613849094898</v>
       </c>
       <c r="E26">
-        <v>-21.90893584483792</v>
+        <v>-23.5754658806726</v>
       </c>
       <c r="F26">
-        <v>0.1981627312175928</v>
+        <v>-1.142599612257575</v>
       </c>
       <c r="G26">
-        <v>-0.9547265614720216</v>
+        <v>-2.010978997400044</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.3610108312138563</v>
       </c>
       <c r="E27">
-        <v>-22.2218387860505</v>
+        <v>-24.21810888180862</v>
       </c>
       <c r="F27">
-        <v>0.6771554131101705</v>
+        <v>-1.198757951962965</v>
       </c>
       <c r="G27">
-        <v>-1.387616732869107</v>
+        <v>-2.79793312875473</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.4364774647932803</v>
       </c>
       <c r="E28">
-        <v>-21.77898601569536</v>
+        <v>-23.83380393149958</v>
       </c>
       <c r="F28">
-        <v>0.3839754800743555</v>
+        <v>-1.372526238783023</v>
       </c>
       <c r="G28">
-        <v>-0.6638321776409971</v>
+        <v>-2.566986662224849</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.4705309261978493</v>
       </c>
       <c r="E29">
-        <v>-21.00100647032848</v>
+        <v>-23.41999456793897</v>
       </c>
       <c r="F29">
-        <v>-0.086717788809574</v>
+        <v>-1.438515642824837</v>
       </c>
       <c r="G29">
-        <v>-1.26718047413646</v>
+        <v>-2.379576972496373</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.4615121510535494</v>
       </c>
       <c r="E30">
-        <v>-20.94642081388626</v>
+        <v>-22.65742758979852</v>
       </c>
       <c r="F30">
-        <v>-0.09590272657181492</v>
+        <v>-1.452917638489909</v>
       </c>
       <c r="G30">
-        <v>-1.332328994663101</v>
+        <v>-2.295226425502094</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.4123150236704225</v>
       </c>
       <c r="E31">
-        <v>-20.76123327412348</v>
+        <v>-23.77896077595522</v>
       </c>
       <c r="F31">
-        <v>0.2697966307420828</v>
+        <v>-1.228991705430341</v>
       </c>
       <c r="G31">
-        <v>-1.266493848308997</v>
+        <v>-2.069169883591368</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.330658758956076</v>
       </c>
       <c r="E32">
-        <v>-21.13878510281834</v>
+        <v>-22.91118880174555</v>
       </c>
       <c r="F32">
-        <v>0.3718084196620364</v>
+        <v>-1.28117885180671</v>
       </c>
       <c r="G32">
-        <v>-2.084032852548576</v>
+        <v>-2.784265880820252</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.2282109417021461</v>
       </c>
       <c r="E33">
-        <v>-20.00824775450942</v>
+        <v>-22.32085965045707</v>
       </c>
       <c r="F33">
-        <v>0.5223095228722617</v>
+        <v>-1.102218358105905</v>
       </c>
       <c r="G33">
-        <v>-1.597478826081157</v>
+        <v>-2.460692806942263</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.1176637540479694</v>
       </c>
       <c r="E34">
-        <v>-18.49760435254085</v>
+        <v>-22.80778214617997</v>
       </c>
       <c r="F34">
-        <v>-0.03209938410598859</v>
+        <v>-0.9853017545073797</v>
       </c>
       <c r="G34">
-        <v>-1.084994884334801</v>
+        <v>-2.405799291169515</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.01087571710774884</v>
       </c>
       <c r="E35">
-        <v>-18.84881651501366</v>
+        <v>-21.88912502681849</v>
       </c>
       <c r="F35">
-        <v>0.2869198133253514</v>
+        <v>-1.043373622913236</v>
       </c>
       <c r="G35">
-        <v>-1.727240664493261</v>
+        <v>-2.766275239842891</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.08360516684812271</v>
       </c>
       <c r="E36">
-        <v>-18.25983715740574</v>
+        <v>-20.45468474623788</v>
       </c>
       <c r="F36">
-        <v>0.06017743109626513</v>
+        <v>-1.152781904372786</v>
       </c>
       <c r="G36">
-        <v>-2.20293921495083</v>
+        <v>-3.224941292588037</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.1609170584854112</v>
       </c>
       <c r="E37">
-        <v>-17.62501465319438</v>
+        <v>-20.3373606795228</v>
       </c>
       <c r="F37">
-        <v>0.4058327823646232</v>
+        <v>-1.284728406127706</v>
       </c>
       <c r="G37">
-        <v>-1.223071944269601</v>
+        <v>-2.956582856067502</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2203004424801449</v>
       </c>
       <c r="E38">
-        <v>-18.18475124986417</v>
+        <v>-20.08114076647148</v>
       </c>
       <c r="F38">
-        <v>-0.3531696192266602</v>
+        <v>-1.100666825960461</v>
       </c>
       <c r="G38">
-        <v>-2.485620196298212</v>
+        <v>-3.062921094008138</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.2658245264948541</v>
       </c>
       <c r="E39">
-        <v>-16.19463621328945</v>
+        <v>-18.98029472592375</v>
       </c>
       <c r="F39">
-        <v>0.03591206476605922</v>
+        <v>-1.061436174131279</v>
       </c>
       <c r="G39">
-        <v>-2.225271524183214</v>
+        <v>-2.974784967356744</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.3027718136323276</v>
       </c>
       <c r="E40">
-        <v>-16.80167788694904</v>
+        <v>-18.50974834245465</v>
       </c>
       <c r="F40">
-        <v>0.2672228932215848</v>
+        <v>-0.85611288783638</v>
       </c>
       <c r="G40">
-        <v>-2.300319988199356</v>
+        <v>-3.376343592915879</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.3418834362512938</v>
       </c>
       <c r="E41">
-        <v>-13.92653843632131</v>
+        <v>-17.23614947685068</v>
       </c>
       <c r="F41">
-        <v>0.3575778960493436</v>
+        <v>-0.9303337787598129</v>
       </c>
       <c r="G41">
-        <v>-2.467446803199473</v>
+        <v>-3.171567230167317</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3922087752237309</v>
       </c>
       <c r="E42">
-        <v>-14.78130255266163</v>
+        <v>-16.86913434528691</v>
       </c>
       <c r="F42">
-        <v>0.4584415677490171</v>
+        <v>-0.925668413547246</v>
       </c>
       <c r="G42">
-        <v>-2.06633722571001</v>
+        <v>-3.656069211386121</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.4658064028405726</v>
       </c>
       <c r="E43">
-        <v>-14.36127583174774</v>
+        <v>-16.48849252736637</v>
       </c>
       <c r="F43">
-        <v>0.1308910144362449</v>
+        <v>-1.134389662928429</v>
       </c>
       <c r="G43">
-        <v>-2.964117464957456</v>
+        <v>-3.422947994611842</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.572836881308957</v>
       </c>
       <c r="E44">
-        <v>-12.96968838561672</v>
+        <v>-15.13641458056844</v>
       </c>
       <c r="F44">
-        <v>-0.2116256527429058</v>
+        <v>-1.017338863810651</v>
       </c>
       <c r="G44">
-        <v>-2.11042486962014</v>
+        <v>-3.512452151428979</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7223199091121966</v>
       </c>
       <c r="E45">
-        <v>-11.35228253333211</v>
+        <v>-15.07994336618475</v>
       </c>
       <c r="F45">
-        <v>0.1321285953360274</v>
+        <v>-1.026725923219175</v>
       </c>
       <c r="G45">
-        <v>-2.947745485626584</v>
+        <v>-3.716455733778571</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.9229227891680091</v>
       </c>
       <c r="E46">
-        <v>-13.01194731084685</v>
+        <v>-14.70642015247497</v>
       </c>
       <c r="F46">
-        <v>0.2652066469631708</v>
+        <v>-0.8717284417465535</v>
       </c>
       <c r="G46">
-        <v>-3.139841461896109</v>
+        <v>-3.90790685613409</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.174582589012228</v>
       </c>
       <c r="E47">
-        <v>-11.18735020520052</v>
+        <v>-13.28699373083361</v>
       </c>
       <c r="F47">
-        <v>0.2951073967346217</v>
+        <v>-1.052509686998712</v>
       </c>
       <c r="G47">
-        <v>-2.757061922180852</v>
+        <v>-4.59431077030664</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.481161657352425</v>
       </c>
       <c r="E48">
-        <v>-10.78483342323211</v>
+        <v>-13.24690693512637</v>
       </c>
       <c r="F48">
-        <v>0.345685853614754</v>
+        <v>-1.040688884160763</v>
       </c>
       <c r="G48">
-        <v>-3.177887842822402</v>
+        <v>-4.689435860228444</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.836648657447876</v>
       </c>
       <c r="E49">
-        <v>-10.96652395905939</v>
+        <v>-12.17715598776763</v>
       </c>
       <c r="F49">
-        <v>0.2845349435726917</v>
+        <v>-1.153693936883269</v>
       </c>
       <c r="G49">
-        <v>-3.340310096069333</v>
+        <v>-4.857460771367903</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.238789740862443</v>
       </c>
       <c r="E50">
-        <v>-9.496486504213674</v>
+        <v>-11.90115017596483</v>
       </c>
       <c r="F50">
-        <v>0.1126694166768642</v>
+        <v>-0.7509135411504539</v>
       </c>
       <c r="G50">
-        <v>-3.617579003879337</v>
+        <v>-4.765578226228262</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.681762855025118</v>
       </c>
       <c r="E51">
-        <v>-8.65392452274571</v>
+        <v>-10.67222325137071</v>
       </c>
       <c r="F51">
-        <v>0.1513094425478499</v>
+        <v>-0.7286594508742453</v>
       </c>
       <c r="G51">
-        <v>-3.339028220475097</v>
+        <v>-5.081726342489126</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.159894444608944</v>
       </c>
       <c r="E52">
-        <v>-9.666398532723736</v>
+        <v>-10.21409912297417</v>
       </c>
       <c r="F52">
-        <v>0.2567142243496702</v>
+        <v>-0.8522850020680435</v>
       </c>
       <c r="G52">
-        <v>-3.568483951843452</v>
+        <v>-4.947071968713276</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.673602196845158</v>
       </c>
       <c r="E53">
-        <v>-8.086861661298919</v>
+        <v>-10.3128458754333</v>
       </c>
       <c r="F53">
-        <v>0.4718254998760487</v>
+        <v>-0.6112300878533874</v>
       </c>
       <c r="G53">
-        <v>-3.687638334981862</v>
+        <v>-5.472471263951869</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.215007569219066</v>
       </c>
       <c r="E54">
-        <v>-7.648108110521382</v>
+        <v>-9.347245008467286</v>
       </c>
       <c r="F54">
-        <v>0.1453584511261383</v>
+        <v>-0.6731662901933035</v>
       </c>
       <c r="G54">
-        <v>-3.486558786574317</v>
+        <v>-5.868821454051733</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.789368255921018</v>
       </c>
       <c r="E55">
-        <v>-7.530293964869971</v>
+        <v>-9.063962770423382</v>
       </c>
       <c r="F55">
-        <v>0.1873715890613236</v>
+        <v>-0.5285656479932191</v>
       </c>
       <c r="G55">
-        <v>-3.982148600071579</v>
+        <v>-5.901116364643804</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.38993646896911</v>
       </c>
       <c r="E56">
-        <v>-6.566557889788808</v>
+        <v>-8.551834435170099</v>
       </c>
       <c r="F56">
-        <v>-0.2609052295354484</v>
+        <v>-0.5885112834642081</v>
       </c>
       <c r="G56">
-        <v>-4.498566933916742</v>
+        <v>-6.006924621432443</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.017905957158083</v>
       </c>
       <c r="E57">
-        <v>-6.5407124557144</v>
+        <v>-8.132841863876095</v>
       </c>
       <c r="F57">
-        <v>0.08612355488675125</v>
+        <v>-0.5364798701595656</v>
       </c>
       <c r="G57">
-        <v>-4.467099629360054</v>
+        <v>-6.074597731978691</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.669160106822127</v>
       </c>
       <c r="E58">
-        <v>-6.409379607200671</v>
+        <v>-6.784701161414102</v>
       </c>
       <c r="F58">
-        <v>0.269911773811072</v>
+        <v>-0.6430775010214171</v>
       </c>
       <c r="G58">
-        <v>-5.22623888784102</v>
+        <v>-6.703471278341468</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.337305067767351</v>
       </c>
       <c r="E59">
-        <v>-6.077122701214388</v>
+        <v>-7.510242260593699</v>
       </c>
       <c r="F59">
-        <v>0.04103137531536016</v>
+        <v>-0.5319296480159879</v>
       </c>
       <c r="G59">
-        <v>-5.721267391251192</v>
+        <v>-6.585486508779876</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.022120845760352</v>
       </c>
       <c r="E60">
-        <v>-4.599165072372227</v>
+        <v>-6.697915657570484</v>
       </c>
       <c r="F60">
-        <v>0.4120380825789943</v>
+        <v>-0.5918114991969613</v>
       </c>
       <c r="G60">
-        <v>-5.480663780478783</v>
+        <v>-6.697409129400903</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.710223363259045</v>
       </c>
       <c r="E61">
-        <v>-5.736326792744257</v>
+        <v>-6.298999709820703</v>
       </c>
       <c r="F61">
-        <v>0.1464742620177092</v>
+        <v>-0.6293564233614461</v>
       </c>
       <c r="G61">
-        <v>-5.817525544325539</v>
+        <v>-7.095542458056497</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.401190227333135</v>
       </c>
       <c r="E62">
-        <v>-4.174881309850393</v>
+        <v>-5.90450277892054</v>
       </c>
       <c r="F62">
-        <v>-0.06975365276764292</v>
+        <v>-0.9951154231283454</v>
       </c>
       <c r="G62">
-        <v>-5.35381292228577</v>
+        <v>-7.298162345772798</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.0788715408656</v>
       </c>
       <c r="E63">
-        <v>-4.049466787474546</v>
+        <v>-5.160214083820666</v>
       </c>
       <c r="F63">
-        <v>-0.1903838274329181</v>
+        <v>-0.6248020593808544</v>
       </c>
       <c r="G63">
-        <v>-5.539538681752978</v>
+        <v>-7.499348934708579</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.73552909951114</v>
       </c>
       <c r="E64">
-        <v>-3.463390524582691</v>
+        <v>-5.104311859388473</v>
       </c>
       <c r="F64">
-        <v>-0.2947183585503215</v>
+        <v>-1.021059061816623</v>
       </c>
       <c r="G64">
-        <v>-5.644148606774297</v>
+        <v>-7.281343929116847</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.35732547112295</v>
       </c>
       <c r="E65">
-        <v>-4.021175111929814</v>
+        <v>-4.583171055560313</v>
       </c>
       <c r="F65">
-        <v>-0.1903167296732914</v>
+        <v>-0.736986200007186</v>
       </c>
       <c r="G65">
-        <v>-5.48926357316191</v>
+        <v>-7.557503270475628</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.93047630524999</v>
       </c>
       <c r="E66">
-        <v>-3.241031743462696</v>
+        <v>-5.635877223641954</v>
       </c>
       <c r="F66">
-        <v>-0.2787822264552646</v>
+        <v>-1.035540580752364</v>
       </c>
       <c r="G66">
-        <v>-6.110069918738147</v>
+        <v>-7.769312979152649</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.44707908362374</v>
       </c>
       <c r="E67">
-        <v>-3.769187321218492</v>
+        <v>-5.26694330844611</v>
       </c>
       <c r="F67">
-        <v>0.06368639541452384</v>
+        <v>-1.037004305953111</v>
       </c>
       <c r="G67">
-        <v>-6.274533774255328</v>
+        <v>-7.800803780410657</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.89252694612954</v>
       </c>
       <c r="E68">
-        <v>-4.230264382866983</v>
+        <v>-5.084064954179935</v>
       </c>
       <c r="F68">
-        <v>-0.5070927081778503</v>
+        <v>-1.096979762650601</v>
       </c>
       <c r="G68">
-        <v>-5.533359049305814</v>
+        <v>-7.758303469211924</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.26629494317772</v>
       </c>
       <c r="E69">
-        <v>-3.404867623804532</v>
+        <v>-4.962878400932762</v>
       </c>
       <c r="F69">
-        <v>-0.3569552582574539</v>
+        <v>-1.242097306110032</v>
       </c>
       <c r="G69">
-        <v>-6.658887592959026</v>
+        <v>-7.580013110340206</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.55936566682818</v>
       </c>
       <c r="E70">
-        <v>-4.204119917577186</v>
+        <v>-4.790200333680366</v>
       </c>
       <c r="F70">
-        <v>-0.4770726735003962</v>
+        <v>-1.076527371475481</v>
       </c>
       <c r="G70">
-        <v>-6.363502728431287</v>
+        <v>-7.362592911536884</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.77613230540892</v>
       </c>
       <c r="E71">
-        <v>-2.953704277588408</v>
+        <v>-4.465514731939245</v>
       </c>
       <c r="F71">
-        <v>-0.7813237368746266</v>
+        <v>-1.142347788567124</v>
       </c>
       <c r="G71">
-        <v>-5.754426458302921</v>
+        <v>-7.307237293971508</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.91688171864298</v>
       </c>
       <c r="E72">
-        <v>-3.935365612747532</v>
+        <v>-5.217922955179159</v>
       </c>
       <c r="F72">
-        <v>-0.9449014479054451</v>
+        <v>-1.102059311564567</v>
       </c>
       <c r="G72">
-        <v>-4.998521912370346</v>
+        <v>-7.642079646877039</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.98786699456126</v>
       </c>
       <c r="E73">
-        <v>-4.10654852392299</v>
+        <v>-4.988914882728112</v>
       </c>
       <c r="F73">
-        <v>-1.016756521526482</v>
+        <v>-1.295057319273213</v>
       </c>
       <c r="G73">
-        <v>-5.070703778825446</v>
+        <v>-7.248237076956939</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.99607802458509</v>
       </c>
       <c r="E74">
-        <v>-5.12366167095085</v>
+        <v>-4.428650828220067</v>
       </c>
       <c r="F74">
-        <v>-1.276134922691064</v>
+        <v>-1.300645485772498</v>
       </c>
       <c r="G74">
-        <v>-5.414437022436012</v>
+        <v>-7.5370350328813</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.94609739644932</v>
       </c>
       <c r="E75">
-        <v>-3.30246604537956</v>
+        <v>-5.377368891150651</v>
       </c>
       <c r="F75">
-        <v>-0.5431954446940611</v>
+        <v>-1.30557261508435</v>
       </c>
       <c r="G75">
-        <v>-4.603495369778177</v>
+        <v>-7.409904825017039</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.84756129722105</v>
       </c>
       <c r="E76">
-        <v>-6.105995826344595</v>
+        <v>-6.052797342484867</v>
       </c>
       <c r="F76">
-        <v>-0.8358046325893473</v>
+        <v>-1.205320278527942</v>
       </c>
       <c r="G76">
-        <v>-5.314119161522484</v>
+        <v>-7.007813607561317</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.70006787669857</v>
       </c>
       <c r="E77">
-        <v>-5.152655239209478</v>
+        <v>-6.400317300089895</v>
       </c>
       <c r="F77">
-        <v>-0.7031507050724373</v>
+        <v>-1.43331763737227</v>
       </c>
       <c r="G77">
-        <v>-4.669727349310129</v>
+        <v>-6.534065283313309</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.51092997379246</v>
       </c>
       <c r="E78">
-        <v>-6.130840336489721</v>
+        <v>-7.129737498646882</v>
       </c>
       <c r="F78">
-        <v>-0.9932698205549082</v>
+        <v>-1.64524549696969</v>
       </c>
       <c r="G78">
-        <v>-4.534697028313159</v>
+        <v>-6.295364905347821</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.27457034514628</v>
       </c>
       <c r="E79">
-        <v>-6.051244041449381</v>
+        <v>-6.53304978082009</v>
       </c>
       <c r="F79">
-        <v>-1.137605385186097</v>
+        <v>-1.238696029554137</v>
       </c>
       <c r="G79">
-        <v>-4.431368978886078</v>
+        <v>-5.785953809985206</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.99217079980364</v>
       </c>
       <c r="E80">
-        <v>-8.259199165222679</v>
+        <v>-7.559358137721121</v>
       </c>
       <c r="F80">
-        <v>-0.4481783901233466</v>
+        <v>-1.183877988306477</v>
       </c>
       <c r="G80">
-        <v>-3.884780880546009</v>
+        <v>-6.031486506545637</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.65593429007181</v>
       </c>
       <c r="E81">
-        <v>-8.892817238149847</v>
+        <v>-9.227503772761155</v>
       </c>
       <c r="F81">
-        <v>-1.22844995314891</v>
+        <v>-1.259169129914327</v>
       </c>
       <c r="G81">
-        <v>-3.381442377102323</v>
+        <v>-5.077301130407188</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.26273286792959</v>
       </c>
       <c r="E82">
-        <v>-9.933258973189268</v>
+        <v>-9.058538676433155</v>
       </c>
       <c r="F82">
-        <v>-0.9261389262320362</v>
+        <v>-1.405273258950493</v>
       </c>
       <c r="G82">
-        <v>-3.289256985590113</v>
+        <v>-5.073967209564337</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.81109022897736</v>
       </c>
       <c r="E83">
-        <v>-8.870626630041288</v>
+        <v>-10.58608980170509</v>
       </c>
       <c r="F83">
-        <v>-1.208030696669902</v>
+        <v>-1.360512426340221</v>
       </c>
       <c r="G83">
-        <v>-2.65628979170847</v>
+        <v>-4.509667819918156</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.29702539534069</v>
       </c>
       <c r="E84">
-        <v>-10.80683713683105</v>
+        <v>-11.71660223074607</v>
       </c>
       <c r="F84">
-        <v>-0.8209097583196094</v>
+        <v>-1.168608691970674</v>
       </c>
       <c r="G84">
-        <v>-2.897697511814942</v>
+        <v>-4.189368619757422</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.7286931039787</v>
       </c>
       <c r="E85">
-        <v>-11.91777548089812</v>
+        <v>-12.51558456578261</v>
       </c>
       <c r="F85">
-        <v>-0.8688738876765064</v>
+        <v>-1.379214477193226</v>
       </c>
       <c r="G85">
-        <v>-2.141839959285006</v>
+        <v>-3.962573237127411</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.1050045347069</v>
       </c>
       <c r="E86">
-        <v>-12.66319384947834</v>
+        <v>-13.5642164335546</v>
       </c>
       <c r="F86">
-        <v>-0.9935705179221244</v>
+        <v>-1.104958597474365</v>
       </c>
       <c r="G86">
-        <v>-2.263518932443023</v>
+        <v>-3.45094300886235</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.44023286272216</v>
       </c>
       <c r="E87">
-        <v>-15.44111908262581</v>
+        <v>-14.43737512285257</v>
       </c>
       <c r="F87">
-        <v>-1.013882086638768</v>
+        <v>-1.54969414542417</v>
       </c>
       <c r="G87">
-        <v>-2.273818319854965</v>
+        <v>-3.645401708986832</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.740991998293916</v>
       </c>
       <c r="E88">
-        <v>-16.28530912293311</v>
+        <v>-14.95915136801343</v>
       </c>
       <c r="F88">
-        <v>-1.076184427370722</v>
+        <v>-1.582031952094657</v>
       </c>
       <c r="G88">
-        <v>-1.797524519630622</v>
+        <v>-2.98190446785671</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.024030274835363</v>
       </c>
       <c r="E89">
-        <v>-17.61169945768698</v>
+        <v>-17.14034735122086</v>
       </c>
       <c r="F89">
-        <v>-1.330803029438817</v>
+        <v>-1.6522907617305</v>
       </c>
       <c r="G89">
-        <v>-2.28307079868587</v>
+        <v>-2.962498803310965</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.307456025657486</v>
       </c>
       <c r="E90">
-        <v>-19.79819909175621</v>
+        <v>-18.6078638067924</v>
       </c>
       <c r="F90">
-        <v>-0.9678646206784501</v>
+        <v>-1.326363808527214</v>
       </c>
       <c r="G90">
-        <v>-1.162531387946275</v>
+        <v>-2.424118885965357</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.608270128450692</v>
       </c>
       <c r="E91">
-        <v>-21.3802071239193</v>
+        <v>-20.6766115933801</v>
       </c>
       <c r="F91">
-        <v>-1.323112466471227</v>
+        <v>-1.599724223083649</v>
       </c>
       <c r="G91">
-        <v>-1.174446826260116</v>
+        <v>-2.264202947525895</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.954155649669588</v>
       </c>
       <c r="E92">
-        <v>-22.48648971809123</v>
+        <v>-22.45533647994369</v>
       </c>
       <c r="F92">
-        <v>-0.8091270603821893</v>
+        <v>-1.608714494506232</v>
       </c>
       <c r="G92">
-        <v>-1.136938258719591</v>
+        <v>-2.523977255830849</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.361398564241288</v>
       </c>
       <c r="E93">
-        <v>-22.4951990022394</v>
+        <v>-24.05785722284011</v>
       </c>
       <c r="F93">
-        <v>-1.47667852907181</v>
+        <v>-1.975960413761156</v>
       </c>
       <c r="G93">
-        <v>-1.466009560706465</v>
+        <v>-2.025841966357252</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.854728997230128</v>
       </c>
       <c r="E94">
-        <v>-26.97552555743408</v>
+        <v>-26.25615197707186</v>
       </c>
       <c r="F94">
-        <v>-1.601168067466728</v>
+        <v>-1.916944206516108</v>
       </c>
       <c r="G94">
-        <v>-1.415747505838352</v>
+        <v>-2.219796792775649</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.445842929804539</v>
       </c>
       <c r="E95">
-        <v>-28.08637460745766</v>
+        <v>-28.51763368839955</v>
       </c>
       <c r="F95">
-        <v>-1.864552453391248</v>
+        <v>-2.124787386450324</v>
       </c>
       <c r="G95">
-        <v>-0.8692716695157016</v>
+        <v>-2.549139612199999</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.142933802405594</v>
       </c>
       <c r="E96">
-        <v>-31.72037429511843</v>
+        <v>-30.72906712665739</v>
       </c>
       <c r="F96">
-        <v>-2.306163399497692</v>
+        <v>-2.260169956192055</v>
       </c>
       <c r="G96">
-        <v>-1.25540862677513</v>
+        <v>-1.980524661744707</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.945818740254754</v>
       </c>
       <c r="E97">
-        <v>-32.18677992689667</v>
+        <v>-32.97137138469268</v>
       </c>
       <c r="F97">
-        <v>-1.914228818169731</v>
+        <v>-2.423084144933231</v>
       </c>
       <c r="G97">
-        <v>-1.601005942023751</v>
+        <v>-2.871261112085329</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.841895288980225</v>
       </c>
       <c r="E98">
-        <v>-34.74180646145192</v>
+        <v>-34.46419751007772</v>
       </c>
       <c r="F98">
-        <v>-2.460631554199924</v>
+        <v>-2.842245506056406</v>
       </c>
       <c r="G98">
-        <v>-2.054293860911204</v>
+        <v>-2.736802544153813</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.815816518546072</v>
       </c>
       <c r="E99">
-        <v>-38.93598090957724</v>
+        <v>-37.15101997620942</v>
       </c>
       <c r="F99">
-        <v>-1.97294349968016</v>
+        <v>-2.821045099116558</v>
       </c>
       <c r="G99">
-        <v>-2.973490038039552</v>
+        <v>-2.983773760983947</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.840978318235726</v>
       </c>
       <c r="E100">
-        <v>-40.29583574458091</v>
+        <v>-39.71586054912523</v>
       </c>
       <c r="F100">
-        <v>-2.648195471746205</v>
+        <v>-3.13628611282373</v>
       </c>
       <c r="G100">
-        <v>-2.546403551868512</v>
+        <v>-3.157396108526754</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.889796146234833</v>
       </c>
       <c r="E101">
-        <v>-42.98653731008999</v>
+        <v>-41.61442011864977</v>
       </c>
       <c r="F101">
-        <v>-2.740074670595115</v>
+        <v>-3.149161427365442</v>
       </c>
       <c r="G101">
-        <v>-2.6201753617796</v>
+        <v>-3.091451310899824</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.936690878062716</v>
       </c>
       <c r="E102">
-        <v>-44.0575715997481</v>
+        <v>-44.03706511883176</v>
       </c>
       <c r="F102">
-        <v>-2.724266935447492</v>
+        <v>-3.215768793489745</v>
       </c>
       <c r="G102">
-        <v>-3.23618054805278</v>
+        <v>-3.821125705925485</v>
       </c>
     </row>
   </sheetData>
